--- a/Claude outputs/POTATO_SURVIVORS_QA_테스트케이스.xlsx
+++ b/Claude outputs/POTATO_SURVIVORS_QA_테스트케이스.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="304">
   <si>
     <r>
       <rPr>
@@ -653,6 +653,42 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">첫 무기 기본 선택으로 유지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">빈손 시작 없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">TC-005</t>
   </si>
   <si>
@@ -780,6 +816,42 @@
     <t xml:space="preserve">카메라 화면 경계를 벗어나지 않음</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">★2026-09-07 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">화면 경계 여백 → 재검증</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">TC-008</t>
   </si>
   <si>
@@ -1206,6 +1278,76 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">★2026-09-07 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보스 배선</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">스테이지 등장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">재검증</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">TC-019</t>
   </si>
   <si>
@@ -1681,6 +1823,42 @@
     <t xml:space="preserve">코인이 흡수되어 골드 증가</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">★2026-09-07 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">코인 자석 범위 확대 → 재검증</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">TC-029</t>
   </si>
   <si>
@@ -2142,6 +2320,45 @@
     <t xml:space="preserve">만렙 무기 카드가 남은 경우</t>
   </si>
   <si>
+    <t xml:space="preserve">N/A</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만렙 무기는 상점 미노출 → 도달 불가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">설계상 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">N/A)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">TC-038</t>
   </si>
   <si>
@@ -2987,6 +3204,76 @@
     <t xml:space="preserve">장착 무기 아이콘이 줄로 표시</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">★2026-09-07 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상점 풀 정리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아이콘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">재검증</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">TC-052</t>
   </si>
   <si>
@@ -3205,9 +3492,6 @@
   </si>
   <si>
     <t xml:space="preserve">Fail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N/A</t>
   </si>
   <si>
     <t xml:space="preserve">보류</t>
@@ -3386,7 +3670,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3402,13 +3686,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF6DA"/>
-        <bgColor rgb="FFF2F5F8"/>
+        <bgColor rgb="FFFFF0D0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F5F8"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF0D0"/>
+        <bgColor rgb="FFFFF6DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -3461,7 +3751,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3520,6 +3810,10 @@
     </xf>
     <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -3616,7 +3910,7 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFFFF0D0"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -3989,7 +4283,7 @@
       <c r="H7" s="7"/>
       <c r="I7" s="10"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
         <v>36</v>
       </c>
@@ -4010,26 +4304,28 @@
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="7"/>
-      <c r="I8" s="10"/>
+      <c r="I8" s="9" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>21</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G9" s="10"/>
       <c r="H9" s="7"/>
@@ -4037,53 +4333,55 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="7"/>
       <c r="I10" s="10"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>50</v>
+    <row r="11" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="15" t="s">
+        <v>51</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="7"/>
-      <c r="I11" s="10"/>
+      <c r="I11" s="10" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>12</v>
@@ -4092,13 +4390,13 @@
         <v>13</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G12" s="10"/>
       <c r="H12" s="7"/>
@@ -4106,22 +4404,22 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G13" s="10"/>
       <c r="H13" s="7"/>
@@ -4129,22 +4427,22 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G14" s="10"/>
       <c r="H14" s="7"/>
@@ -4152,22 +4450,22 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G15" s="10"/>
       <c r="H15" s="7"/>
@@ -4175,22 +4473,22 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G16" s="10"/>
       <c r="H16" s="7"/>
@@ -4198,22 +4496,22 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G17" s="10"/>
       <c r="H17" s="7"/>
@@ -4221,22 +4519,22 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G18" s="10"/>
       <c r="H18" s="7"/>
@@ -4244,22 +4542,22 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G19" s="10"/>
       <c r="H19" s="7"/>
@@ -4267,22 +4565,22 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G20" s="10"/>
       <c r="H20" s="7"/>
@@ -4290,68 +4588,70 @@
     </row>
     <row r="21" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G21" s="10"/>
       <c r="H21" s="7"/>
       <c r="I21" s="10"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="s">
-        <v>104</v>
+    <row r="22" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="15" t="s">
+        <v>106</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G22" s="10"/>
       <c r="H22" s="7"/>
-      <c r="I22" s="10"/>
+      <c r="I22" s="10" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G23" s="10"/>
       <c r="H23" s="7"/>
@@ -4359,22 +4659,22 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G24" s="10"/>
       <c r="H24" s="7"/>
@@ -4382,22 +4682,22 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="D25" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>118</v>
-      </c>
       <c r="E25" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G25" s="10"/>
       <c r="H25" s="7"/>
@@ -4405,22 +4705,22 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G26" s="10"/>
       <c r="H26" s="7"/>
@@ -4428,22 +4728,22 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>132</v>
+        <v>134</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>135</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G27" s="10"/>
       <c r="H27" s="7"/>
@@ -4451,22 +4751,22 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G28" s="10"/>
       <c r="H28" s="7"/>
@@ -4474,22 +4774,22 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G29" s="10"/>
       <c r="H29" s="7"/>
@@ -4497,22 +4797,22 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D30" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B30" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>145</v>
-      </c>
       <c r="E30" s="14" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G30" s="10"/>
       <c r="H30" s="7"/>
@@ -4520,68 +4820,70 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G31" s="10"/>
       <c r="H31" s="7"/>
       <c r="I31" s="10"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="11" t="s">
-        <v>157</v>
+    <row r="32" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="15" t="s">
+        <v>160</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G32" s="10"/>
       <c r="H32" s="7"/>
-      <c r="I32" s="10"/>
+      <c r="I32" s="10" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>163</v>
+        <v>156</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>167</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G33" s="10"/>
       <c r="H33" s="7"/>
@@ -4589,22 +4891,22 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="G34" s="10"/>
       <c r="H34" s="7"/>
@@ -4612,22 +4914,22 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G35" s="10"/>
       <c r="H35" s="7"/>
@@ -4635,22 +4937,22 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D36" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="E36" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="E36" s="13" t="s">
-        <v>176</v>
-      </c>
       <c r="F36" s="14" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G36" s="10"/>
       <c r="H36" s="7"/>
@@ -4658,22 +4960,22 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G37" s="10"/>
       <c r="H37" s="7"/>
@@ -4681,22 +4983,22 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G38" s="10"/>
       <c r="H38" s="7"/>
@@ -4704,22 +5006,22 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G39" s="10"/>
       <c r="H39" s="7"/>
@@ -4727,68 +5029,72 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="G40" s="10"/>
       <c r="H40" s="7"/>
       <c r="I40" s="10"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D41" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="E41" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="E41" s="9" t="s">
-        <v>199</v>
-      </c>
       <c r="F41" s="9" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="G41" s="10"/>
-      <c r="H41" s="7"/>
-      <c r="I41" s="10"/>
+      <c r="H41" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="G42" s="10"/>
       <c r="H42" s="7"/>
@@ -4796,22 +5102,22 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="G43" s="10"/>
       <c r="H43" s="7"/>
@@ -4819,22 +5125,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="C44" s="16" t="s">
-        <v>214</v>
+        <v>172</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>220</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="G44" s="10"/>
       <c r="H44" s="7"/>
@@ -4842,22 +5148,22 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="G45" s="10"/>
       <c r="H45" s="7"/>
@@ -4865,22 +5171,22 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="G46" s="10"/>
       <c r="H46" s="7"/>
@@ -4888,22 +5194,22 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="G47" s="10"/>
       <c r="H47" s="7"/>
@@ -4911,22 +5217,22 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="G48" s="10"/>
       <c r="H48" s="7"/>
@@ -4934,22 +5240,22 @@
     </row>
     <row r="49" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="G49" s="10"/>
       <c r="H49" s="7"/>
@@ -4957,22 +5263,22 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="11" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="G50" s="10"/>
       <c r="H50" s="7"/>
@@ -4980,22 +5286,22 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="G51" s="10"/>
       <c r="H51" s="7"/>
@@ -5003,22 +5309,22 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="11" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="G52" s="10"/>
       <c r="H52" s="7"/>
@@ -5026,22 +5332,22 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="G53" s="10"/>
       <c r="H53" s="7"/>
@@ -5049,114 +5355,118 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="B54" s="16" t="s">
-        <v>260</v>
+        <v>265</v>
+      </c>
+      <c r="B54" s="17" t="s">
+        <v>266</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G54" s="10"/>
       <c r="H54" s="7"/>
       <c r="I54" s="10"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="B55" s="15" t="s">
-        <v>260</v>
+    <row r="55" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>266</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="G55" s="10"/>
       <c r="H55" s="7"/>
-      <c r="I55" s="10"/>
+      <c r="I55" s="10" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="B56" s="16" t="s">
-        <v>260</v>
+        <v>277</v>
+      </c>
+      <c r="B56" s="17" t="s">
+        <v>266</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="G56" s="10"/>
       <c r="H56" s="7"/>
       <c r="I56" s="10"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="7" t="s">
-        <v>275</v>
+    <row r="57" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="15" t="s">
+        <v>282</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="G57" s="10"/>
       <c r="H57" s="7"/>
-      <c r="I57" s="10"/>
+      <c r="I57" s="10" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C58" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="E58" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="B58" s="12" t="s">
-        <v>276</v>
-      </c>
-      <c r="C58" s="16" t="s">
-        <v>281</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="E58" s="13" t="s">
-        <v>273</v>
-      </c>
       <c r="F58" s="13" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="G58" s="10"/>
       <c r="H58" s="7"/>
@@ -5164,22 +5474,22 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="G59" s="10"/>
       <c r="H59" s="7"/>
@@ -5221,210 +5531,210 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>290</v>
+      <c r="A1" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="19" t="s">
-        <v>291</v>
+      <c r="E2" s="20" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
-        <v>292</v>
-      </c>
-      <c r="B3" s="20" t="n">
+      <c r="A3" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="B3" s="21" t="n">
         <f aca="false">COUNTA('테스트 케이스'!A5:A59)</f>
         <v>55</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="21" t="n">
+      <c r="E3" s="22" t="n">
         <f aca="false">COUNTIF('테스트 케이스'!B5:B59,D3)</f>
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="23" t="n">
+      <c r="B4" s="24" t="n">
         <f aca="false">COUNTIF('테스트 케이스'!H5:H59,"Pass")</f>
         <v>0</v>
       </c>
-      <c r="D4" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" s="21" t="n">
+      <c r="D4" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="22" t="n">
         <f aca="false">COUNTIF('테스트 케이스'!B5:B59,D4)</f>
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
-        <v>293</v>
-      </c>
-      <c r="B5" s="23" t="n">
+      <c r="A5" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="B5" s="24" t="n">
         <f aca="false">COUNTIF('테스트 케이스'!H5:H59,"Fail")</f>
         <v>0</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="21" t="n">
+      <c r="E5" s="22" t="n">
         <f aca="false">COUNTIF('테스트 케이스'!B5:B59,D5)</f>
         <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="s">
-        <v>294</v>
-      </c>
-      <c r="B6" s="23" t="n">
+      <c r="A6" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="B6" s="24" t="n">
         <f aca="false">COUNTIF('테스트 케이스'!H5:H59,"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" s="22" t="n">
         <f aca="false">COUNTIF('테스트 케이스'!B5:B59,D6)</f>
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
-        <v>295</v>
-      </c>
-      <c r="B7" s="23" t="n">
+      <c r="A7" s="25" t="s">
+        <v>301</v>
+      </c>
+      <c r="B7" s="24" t="n">
         <f aca="false">COUNTIF('테스트 케이스'!H5:H59,"보류")</f>
         <v>0</v>
       </c>
-      <c r="D7" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="E7" s="21" t="n">
+      <c r="D7" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="22" t="n">
         <f aca="false">COUNTIF('테스트 케이스'!B5:B59,D7)</f>
         <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
-        <v>296</v>
-      </c>
-      <c r="B8" s="23" t="n">
+      <c r="A8" s="25" t="s">
+        <v>302</v>
+      </c>
+      <c r="B8" s="24" t="n">
         <f aca="false">COUNTA('테스트 케이스'!A5:A59)-COUNTA('테스트 케이스'!H5:H59)</f>
-        <v>55</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="E8" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="E8" s="22" t="n">
         <f aca="false">COUNTIF('테스트 케이스'!B5:B59,D8)</f>
         <v>2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D9" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="E9" s="21" t="n">
+      <c r="D9" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="E9" s="22" t="n">
         <f aca="false">COUNTIF('테스트 케이스'!B5:B59,D9)</f>
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D10" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="E10" s="25" t="n">
+      <c r="D10" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="E10" s="26" t="n">
         <f aca="false">COUNTIF('테스트 케이스'!B5:B59,D10)</f>
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="s">
-        <v>297</v>
-      </c>
-      <c r="B11" s="26" t="n">
+      <c r="A11" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="B11" s="27" t="n">
         <f aca="false">IF(B3=0,0,B4/B3)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="E11" s="25" t="n">
+      <c r="D11" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="E11" s="26" t="n">
         <f aca="false">COUNTIF('테스트 케이스'!B5:B59,D11)</f>
         <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D12" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="E12" s="25" t="n">
+      <c r="D12" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="E12" s="26" t="n">
         <f aca="false">COUNTIF('테스트 케이스'!B5:B59,D12)</f>
         <v>2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D13" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="E13" s="25" t="n">
+      <c r="D13" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="E13" s="26" t="n">
         <f aca="false">COUNTIF('테스트 케이스'!B5:B59,D13)</f>
         <v>3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D14" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="E14" s="25" t="n">
+      <c r="D14" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="E14" s="26" t="n">
         <f aca="false">COUNTIF('테스트 케이스'!B5:B59,D14)</f>
         <v>16</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="E15" s="25" t="n">
+      <c r="D15" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="E15" s="26" t="n">
         <f aca="false">COUNTIF('테스트 케이스'!B5:B59,D15)</f>
         <v>4</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="25" t="s">
-        <v>260</v>
-      </c>
-      <c r="E16" s="25" t="n">
+      <c r="D16" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="E16" s="26" t="n">
         <f aca="false">COUNTIF('테스트 케이스'!B5:B59,D16)</f>
         <v>3</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="E17" s="25" t="n">
+      <c r="D17" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="E17" s="26" t="n">
         <f aca="false">COUNTIF('테스트 케이스'!B5:B59,D17)</f>
         <v>2</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="21" t="s">
-        <v>284</v>
-      </c>
-      <c r="E18" s="25" t="n">
+      <c r="D18" s="22" t="s">
+        <v>291</v>
+      </c>
+      <c r="E18" s="26" t="n">
         <f aca="false">COUNTIF('테스트 케이스'!B5:B59,D18)</f>
         <v>1</v>
       </c>
